--- a/02_DIA_inicio_2026_analisis_assets/rbd_9695_liceo-polivalente-eugenio-pereira-salas_nt1_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9695_liceo-polivalente-eugenio-pereira-salas_nt1_rubricas.xlsx
@@ -1992,13 +1992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4615F74A-CD17-4CC8-BBDC-B1D8BF6B8E73}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{730F93A1-B20C-440D-A38E-3F3522AFB0BE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E75C8F70-83CC-4876-BDB7-3A4EA6E9F977}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82275E43-1FE4-4093-B0D6-B2446C107FB4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7460707F-4065-47C2-9556-8A0F9363F63E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0EE16243-C9B1-44B8-9322-D7BFB81BB0BD}"/>
 </file>